--- a/교육자료/양식/_담당자용/02_키워드배정표.xlsx
+++ b/교육자료/양식/_담당자용/02_키워드배정표.xlsx
@@ -503,7 +503,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>※ ★ 표시 = 두 브랜드가 같은 키워드를 놓고 겹치는 것. 한 사람만 쓰게 배정하세요. 겹치는 건 인쇄물·아포스티유 2그룹뿐입니다.</t>
+          <t>※ ★ 표시 = 같은 키워드를 두 브랜드가 놓고 겹치는 것 — 한 사람만 쓰게 배정하세요.  ★ 이번 배정(퍼스트디자인·하오디자인·하오스튜디오·윈차이나)에서는 인쇄물 그룹만 실제로 겹칩니다. 아포스티유는 레드트랜스가 미배정이라 윈차이나가 자유롭게 써도 됩니다.</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>★ 겹침</t>
+          <t>이번엔 안 겹침(레드트랜스 미배정)</t>
         </is>
       </c>
       <c r="E10" s="6" t="n"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>★ 겹침</t>
+          <t>이번엔 안 겹침(레드트랜스 미배정)</t>
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
